--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>SLRN</t>
   </si>
@@ -656,65 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -745,8 +752,14 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +790,14 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +828,14 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,40 +848,48 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>83400</v>
+      </c>
+      <c r="F12" s="3">
         <v>74600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>167900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>12500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>12700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>13000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +920,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +958,14 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +996,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,40 +1013,48 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>105100</v>
+      </c>
+      <c r="F17" s="3">
         <v>94400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>42700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>179800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>15400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>16100</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1003,31 +1062,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-94400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-42700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-179800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-15400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-16100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1105,10 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1049,52 +1116,58 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>10500</v>
+      </c>
+      <c r="G20" s="3">
         <v>16700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="E21" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>-14400</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1177,14 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,40 +1215,52 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-83900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-26000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-176500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-14400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-14500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-16100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1291,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1329,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-83900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-26000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-176500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-14500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-16100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-83900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-26000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-176500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-14500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-16100</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1443,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1481,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1519,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1557,14 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1433,63 +1572,75 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-16700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-83900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-26000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-176500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-14500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-16100</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1671,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-83900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-26000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-176500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-14500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-16100</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1772,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,26 +1788,28 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>264500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>218100</v>
+      </c>
+      <c r="F41" s="3">
         <v>381700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>556200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>289200</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1649,25 +1822,31 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>503200</v>
+      </c>
+      <c r="F42" s="3">
         <v>406700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>266800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+      <c r="H42" s="3">
+        <v>0</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1681,26 +1860,32 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>2000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,8 +1898,14 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,26 +1936,32 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F45" s="3">
         <v>4300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,26 +1974,32 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>694000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>736600</v>
+      </c>
+      <c r="F46" s="3">
         <v>794600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>829800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>291900</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,8 +2012,14 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,26 +2050,32 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1873,8 +2088,14 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1905,8 +2126,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2164,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,26 +2202,32 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2001,8 +2240,14 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,26 +2278,32 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>697500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>742700</v>
+      </c>
+      <c r="F54" s="3">
         <v>800500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>835100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>298500</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2065,8 +2316,14 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2336,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,26 +2352,28 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F57" s="3">
         <v>18700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,8 +2386,14 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2157,26 +2424,32 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>43200</v>
+      </c>
+      <c r="F59" s="3">
         <v>48200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>23600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>22900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,26 +2462,32 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>85200</v>
+      </c>
+      <c r="F60" s="3">
         <v>66900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>33700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2221,8 +2500,14 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2253,26 +2538,32 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>11600</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,8 +2576,14 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2614,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2652,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,26 +2690,32 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>86400</v>
+      </c>
+      <c r="F66" s="3">
         <v>68100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>45300</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2413,8 +2728,14 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2748,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2782,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2820,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2503,14 +2838,14 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>396600</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2523,8 +2858,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,26 +2896,32 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-523700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-488700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-393500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-309600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-283500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,8 +2934,14 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2972,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3010,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,26 +3048,32 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>644100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>656300</v>
+      </c>
+      <c r="F76" s="3">
         <v>732400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>801100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-143400</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2715,8 +3086,14 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3124,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-95200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-83900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-26000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-176500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-14500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-16100</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3225,48 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3297,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3335,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3373,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3411,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3449,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-73600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-39100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-31600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-25300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-14800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-14600</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,25 +3507,27 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-1800</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -3100,8 +3541,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3579,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3617,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-92600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-134800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-267900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>47500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-6900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-102600</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3675,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3709,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3747,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3785,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3823,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>566500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>149800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>125000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3899,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-163600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-174400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>267000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>22100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>128000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-116700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>110400</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>SLRN</t>
   </si>
@@ -656,72 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -758,8 +762,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,8 +803,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E12" s="3">
         <v>58000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>83400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>74600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>167900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,8 +984,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,46 +1041,50 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E17" s="3">
         <v>82800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>105100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>94400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>179800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1062,37 +1092,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-82800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-105100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-94400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-179800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1116,28 +1150,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>47800</v>
+      </c>
+      <c r="F20" s="3">
         <v>9900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>16700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1145,8 +1179,11 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1154,23 +1191,23 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-95200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-83900</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>-14400</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1221,46 +1261,52 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-95200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-83900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-176500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-95200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-83900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-26000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-176500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-95200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-83900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-176500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1572,28 +1642,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-9900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-16700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1601,46 +1671,52 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-95200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-83900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-176500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-95200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-83900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-176500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,29 +1876,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E41" s="3">
         <v>264500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>218100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>381700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>556200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>289200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,28 +1915,31 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E42" s="3">
         <v>414000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>503200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>406700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>266800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1866,29 +1956,32 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1904,8 +1997,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,29 +2038,32 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E45" s="3">
         <v>10100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,29 +2079,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>648300</v>
+      </c>
+      <c r="E46" s="3">
         <v>694000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>736600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>794600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>829800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>291900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,8 +2120,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2056,29 +2161,32 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3400</v>
       </c>
       <c r="F48" s="3">
         <v>3400</v>
       </c>
       <c r="G48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2202,11 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2132,8 +2243,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,29 +2325,32 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,8 +2366,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,29 +2407,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>651700</v>
+      </c>
+      <c r="E54" s="3">
         <v>697500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>742700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>800500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>835100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>298500</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2322,8 +2448,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,29 +2484,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,8 +2523,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2430,29 +2564,32 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E59" s="3">
         <v>42300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2468,29 +2605,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E60" s="3">
         <v>52300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>85200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>66900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33700</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,8 +2646,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2544,8 +2687,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2553,20 +2699,20 @@
         <v>1100</v>
       </c>
       <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1300</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
       </c>
       <c r="H62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I62" s="3">
         <v>11600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2582,8 +2728,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,29 +2851,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E66" s="3">
         <v>53400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>68100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45300</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,8 +2892,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2844,11 +3012,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>396600</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,29 +3073,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-609400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-523700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-488700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-393500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-283500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3114,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,29 +3237,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>568200</v>
+      </c>
+      <c r="E76" s="3">
         <v>644100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>656300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>732400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>801100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-143400</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3278,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-95200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-83900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-176500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,8 +3425,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3236,22 +3435,22 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3259,14 +3458,17 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-57300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-73600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,29 +3729,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,37 +3850,40 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89200</v>
+      </c>
+      <c r="E94" s="3">
         <v>100900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-134800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-267900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>47500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-102600</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3661,8 +3891,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>566500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>149800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>125000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-135700</v>
+      </c>
+      <c r="E102" s="3">
         <v>46400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-163600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-174400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>267000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>22100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>128000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-116700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>110400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>SLRN</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -765,8 +769,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E12" s="3">
         <v>76400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>58000</v>
       </c>
-      <c r="F12" s="3">
-        <v>83400</v>
-      </c>
       <c r="G12" s="3">
+        <v>88400</v>
+      </c>
+      <c r="H12" s="3">
         <v>74600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
-        <v>167900</v>
-      </c>
       <c r="J12" s="3">
+        <v>32400</v>
+      </c>
+      <c r="K12" s="3">
         <v>12500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,31 +963,34 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>10800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-35400</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>-10000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>137800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -987,19 +1007,22 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E17" s="3">
         <v>93000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>82800</v>
       </c>
-      <c r="F17" s="3">
-        <v>105100</v>
-      </c>
       <c r="G17" s="3">
+        <v>109500</v>
+      </c>
+      <c r="H17" s="3">
         <v>94400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42700</v>
       </c>
-      <c r="I17" s="3">
-        <v>179800</v>
-      </c>
       <c r="J17" s="3">
+        <v>41900</v>
+      </c>
+      <c r="K17" s="3">
         <v>15400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-43900</v>
       </c>
       <c r="E18" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-82800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-105100</v>
-      </c>
       <c r="G18" s="3">
+        <v>-109500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-94400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-42700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-179800</v>
-      </c>
       <c r="J18" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,40 +1174,41 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>1300</v>
       </c>
       <c r="E20" s="3">
-        <v>47800</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="3">
-        <v>9900</v>
+        <v>-3300</v>
       </c>
       <c r="G20" s="3">
-        <v>10500</v>
+        <v>5700</v>
       </c>
       <c r="H20" s="3">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>3400</v>
+        <v>-10000</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1182,35 +1216,38 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-45200</v>
       </c>
       <c r="E21" s="3">
-        <v>-34900</v>
+        <v>-94000</v>
       </c>
       <c r="F21" s="3">
-        <v>-95200</v>
+        <v>-79400</v>
       </c>
       <c r="G21" s="3">
-        <v>-83900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>-115200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-94400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-32700</v>
       </c>
       <c r="J21" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-14400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,31 +1260,34 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1264,72 +1304,78 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-85700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-95200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-83900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-176500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-85700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-95200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-83900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-176500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-85700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-95200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-83900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-176500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,40 +1700,43 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-1300</v>
       </c>
       <c r="E32" s="3">
-        <v>-47800</v>
+        <v>-1100</v>
       </c>
       <c r="F32" s="3">
-        <v>-9900</v>
+        <v>3300</v>
       </c>
       <c r="G32" s="3">
-        <v>-10500</v>
+        <v>-5700</v>
       </c>
       <c r="H32" s="3">
-        <v>-16700</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-3400</v>
+        <v>10000</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1674,49 +1744,55 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-85700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-95200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-83900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-176500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-85700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-95200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-83900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-176500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,32 +1963,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>216300</v>
+      </c>
+      <c r="E41" s="3">
         <v>128200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>264500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>218100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>381700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>556200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>289200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,31 +2005,34 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E42" s="3">
         <v>507000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>414000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>503200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>406700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>266800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1959,32 +2049,35 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E43" s="3">
         <v>5500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5400</v>
       </c>
-      <c r="F43" s="3">
-        <v>800</v>
-      </c>
       <c r="G43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H43" s="3">
         <v>2000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,31 +2093,34 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,28 +2137,31 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>14500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2400</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2082,32 +2181,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>596600</v>
+      </c>
+      <c r="E46" s="3">
         <v>648300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>694000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>736600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>794600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>829800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>291900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,31 +2225,34 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2164,32 +2269,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3400</v>
       </c>
       <c r="G48" s="3">
         <v>3400</v>
       </c>
       <c r="H48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2205,8 +2313,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,31 +2445,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>2000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,32 +2533,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>618300</v>
+      </c>
+      <c r="E54" s="3">
         <v>651700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>697500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>742700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>800500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>835100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>298500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2577,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,32 +2615,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E57" s="3">
         <v>40700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,28 +2657,31 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2567,28 +2701,31 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>42300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>43200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>48200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>23600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>22900</v>
+        <v>44600</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2608,32 +2745,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E60" s="3">
         <v>82500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>52300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,31 +2789,34 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2690,31 +2833,34 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>11600</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
+        <v>10300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,32 +3009,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E66" s="3">
         <v>83500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>68100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,8 +3053,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3015,11 +3183,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>396600</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,32 +3247,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-657900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-609400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-523700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-488700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-393500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-309600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-283500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,8 +3291,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,32 +3423,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>528300</v>
+      </c>
+      <c r="E76" s="3">
         <v>568200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>644100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>656300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>732400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>801100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-143400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3467,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-85700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-95200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-83900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-176500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,22 +3624,23 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3449,11 +3648,11 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3461,14 +3660,17 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-46300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-57300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-73600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,32 +3950,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,40 +4080,43 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-92600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-134800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-267900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>47500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-102600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,72 +4318,78 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>566500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>149800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>125000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-135700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-163600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-174400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>267000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>128000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-116700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>110400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>SLRN</t>
   </si>
@@ -656,80 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -754,8 +757,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -772,8 +775,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +890,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E12" s="3">
         <v>31600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>76400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>58000</v>
       </c>
-      <c r="G12" s="3">
-        <v>88400</v>
-      </c>
       <c r="H12" s="3">
+        <v>347500</v>
+      </c>
+      <c r="I12" s="3">
         <v>74600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,35 +982,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E14" s="3">
         <v>10800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-35400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-310100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>137800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1010,8 +1029,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,7 +1047,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E17" s="3">
         <v>43900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>93000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>82800</v>
       </c>
-      <c r="G17" s="3">
-        <v>109500</v>
-      </c>
       <c r="H17" s="3">
+        <v>410300</v>
+      </c>
+      <c r="I17" s="3">
         <v>94400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-73700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-93000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-82800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-109500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-410300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-94400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-42700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,43 +1207,44 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
-        <v>5700</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1219,38 +1252,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-45200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-94000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-79400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-115200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-415400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-94400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1299,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1289,8 +1328,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1307,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-85700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-95200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-83900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-176500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,8 +1422,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-48500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-85700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-95200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-83900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-176500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-85700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-95200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-83900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-176500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,43 +1769,46 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-5700</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-5100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1747,52 +1816,58 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-85700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-95200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-83900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-176500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-85700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-95200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-83900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-176500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,35 +2049,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E41" s="3">
         <v>216300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>128200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>264500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>218100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>556200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>289200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,34 +2094,37 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E42" s="3">
         <v>346000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>507000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>414000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>503200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>406700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>266800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -2052,35 +2141,38 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E43" s="3">
         <v>30100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2188,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2122,8 +2217,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2140,13 +2235,16 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>24300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2184,35 +2282,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E46" s="3">
         <v>596600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>648300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>694000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>736600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>794600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>829800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>291900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2329,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2254,8 +2358,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2272,35 +2376,38 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3400</v>
       </c>
       <c r="H48" s="3">
         <v>3400</v>
       </c>
       <c r="I48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,8 +2423,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2470,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,35 +2564,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>13000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,35 +2658,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>491100</v>
+      </c>
+      <c r="E54" s="3">
         <v>618300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>651700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>697500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>742700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>800500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>835100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>298500</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2705,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,35 +2745,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>17600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>40700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10800</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2660,16 +2790,19 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -2678,14 +2811,14 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2704,17 +2837,20 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>44600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,35 +2884,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E60" s="3">
         <v>83500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>52300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,25 +2931,28 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E61" s="3">
         <v>6600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1100</v>
       </c>
       <c r="F61" s="3">
         <v>1100</v>
       </c>
       <c r="G61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H61" s="3">
         <v>1200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1300</v>
       </c>
       <c r="I61" s="3">
         <v>1300</v>
@@ -2819,7 +2961,7 @@
         <v>1300</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2836,8 +2978,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2859,12 +3004,12 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3025,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,35 +3166,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E66" s="3">
         <v>90000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>68100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3213,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3186,11 +3353,11 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>396600</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,35 +3420,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-736900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-657900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-609400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-523700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-488700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-393500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-309600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-283500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3467,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,35 +3608,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>458300</v>
+      </c>
+      <c r="E76" s="3">
         <v>528300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>568200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>644100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>656300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>732400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>801100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-143400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3655,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-85700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-95200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-83900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-176500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3822,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3636,8 +3834,8 @@
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3651,11 +3849,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3663,14 +3861,17 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-121600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-78800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-46300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-57300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-73600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,35 +4170,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,43 +4309,46 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E94" s="3">
         <v>165900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-89200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-92600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-134800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-267900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>47500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-102600</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4127,8 +4356,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>566500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>149800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>125000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,8 +4639,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-142400</v>
+      </c>
+      <c r="E102" s="3">
         <v>88100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-135700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-163600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-174400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>267000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>128000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-116700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>110400</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>SLRN</t>
   </si>
@@ -656,83 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -760,8 +764,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -778,8 +782,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +832,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E12" s="3">
         <v>62000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>76400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>58000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>347500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>74600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,38 +1002,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>38700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-35400</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-310100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>137800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1032,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,7 +1073,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E17" s="3">
         <v>73700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>93000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>82800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>410300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-59900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-73700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-93000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-82800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-410300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-94400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-42700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,46 +1241,47 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I20" s="3">
         <v>5100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1255,41 +1289,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-46300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-45200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-94000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-79400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-81100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-415400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-94400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1339,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1331,8 +1371,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-79000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-85700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-95200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-83900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-176500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16100</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1425,8 +1471,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-79000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-48500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-85700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-95200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-83900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-176500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16100</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-79000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-48500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-85700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-95200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-83900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-176500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16100</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,46 +1839,49 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>27300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
-        <v>3300</v>
-      </c>
       <c r="H32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1819,55 +1889,61 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-79000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-48500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-85700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-95200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-83900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-176500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16100</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-79000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-48500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-85700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-95200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-83900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-176500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16100</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,38 +2136,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E41" s="3">
         <v>73900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>216300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>128200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>264500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>218100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>381700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>556200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>289200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,37 +2184,40 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>352300</v>
+      </c>
+      <c r="E42" s="3">
         <v>374000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>346000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>507000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>414000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>503200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>406700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>266800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2144,38 +2234,41 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E43" s="3">
         <v>6000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,8 +2284,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2220,8 +2316,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2238,17 +2334,20 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E45" s="3">
         <v>24300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,38 +2384,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>429500</v>
+      </c>
+      <c r="E46" s="3">
         <v>481000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>596600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>648300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>694000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>736600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>794600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>829800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2434,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2361,8 +2466,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2379,38 +2484,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>8400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3400</v>
       </c>
       <c r="I48" s="3">
         <v>3400</v>
       </c>
       <c r="J48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,8 +2534,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,38 +2684,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,38 +2784,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>436500</v>
+      </c>
+      <c r="E54" s="3">
         <v>491100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>618300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>651700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>697500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>742700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>800500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>835100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>298500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2834,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,38 +2876,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,35 +2924,38 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2840,20 +2974,23 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>44600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,38 +3024,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E60" s="3">
         <v>26600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>83500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>52300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,28 +3074,31 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1100</v>
       </c>
       <c r="G61" s="3">
         <v>1100</v>
       </c>
       <c r="H61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I61" s="3">
         <v>1200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1300</v>
       </c>
       <c r="J61" s="3">
         <v>1300</v>
@@ -2964,7 +3107,7 @@
         <v>1300</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2981,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3007,12 +3153,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>10300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,38 +3324,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>83500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>68100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3374,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3356,11 +3524,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>396600</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,38 +3594,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-792200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-736900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-657900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-609400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-523700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-488700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-393500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-309600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-283500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3644,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,38 +3794,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E76" s="3">
         <v>458300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>528300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>568200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>644100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>656300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>732400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>801100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-143400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3844,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-79000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-48500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-85700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-95200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-83900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-176500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16100</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,13 +4021,14 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -3837,8 +4036,8 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3852,11 +4051,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3864,14 +4063,17 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-121600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-78800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-46300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-57300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-73600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-39100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,38 +4391,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,46 +4539,49 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>165900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-89200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-92600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-134800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-267900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>47500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-102600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4359,8 +4589,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4407,8 +4641,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>566500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>149800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>125000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4642,8 +4891,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-142400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>88100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-135700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>46400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-163600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-174400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>267000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>128000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-116700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>110400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
